--- a/output/pdf_financials_xlsx/VVC.xlsx
+++ b/output/pdf_financials_xlsx/VVC.xlsx
@@ -1032,25 +1032,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011632</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1941,25 +1941,25 @@
         <v>-1.792748</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.366796</v>
+        <v>-1.378428</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.9891219999999999</v>
+        <v>-1.001122</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.713655</v>
+        <v>-0.725655</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.493402</v>
+        <v>-1.505402</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.899104</v>
+        <v>-1.911104</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.839545</v>
+        <v>-1.851545</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-14.742</v>
+        <v>-14.751</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-8.405207000000001</v>
@@ -2051,25 +2051,25 @@
         <v>-1.790386</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.361824</v>
+        <v>-1.373456</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.9891219999999999</v>
+        <v>-1.001122</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.713655</v>
+        <v>-0.725655</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.493402</v>
+        <v>-1.505402</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.884157</v>
+        <v>-1.896157</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.806201</v>
+        <v>-1.818201</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-14.735329</v>
+        <v>-14.744329</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-8.404292</v>
@@ -2328,22 +2328,22 @@
         <v>0.09292499999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.513674</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.198811</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.021125</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.18846</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.188448</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.036636</v>
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
@@ -2466,22 +2466,22 @@
         <v>0.09292499999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.513674</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.198811</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.021125</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.18846</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.188448</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.036636</v>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
@@ -3294,13 +3294,13 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.513674</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.198811</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.021125</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -30300,7 +30300,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -30496,7 +30496,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -31534,7 +31534,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -32278,7 +32278,11 @@
           <t>Interest expense (Note 10)(1)</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -32752,7 +32756,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -34272,7 +34276,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -35316,7 +35320,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
